--- a/data/trans_camb/IP16B03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B03-Habitat-trans_camb.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-74,0; 0,0</t>
+          <t>-71,17; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 55,13</t>
+          <t>-24,23; 55,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,38; 57,45</t>
+          <t>-33,47; 57,33</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-74,0; 0,0</t>
+          <t>-71,17; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 119,85</t>
+          <t>-24,35; 128,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,37; 134,8</t>
+          <t>-35,2; 141,36</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,55</t>
+          <t>0,0; 40,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,88</t>
+          <t>0,0; 36,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 8,71</t>
+          <t>-16,88; 8,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 8,75</t>
+          <t>-17,86; 8,49</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,99</t>
+          <t>0,0; 68,54</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,0</t>
+          <t>0,0; 56,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 9,5</t>
+          <t>-16,93; 9,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 9,55</t>
+          <t>-18,33; 9,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B03-Habitat-trans_camb.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-71,17; 0,0</t>
+          <t>-70,17; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 55,91</t>
+          <t>-24,74; 56,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,47; 57,33</t>
+          <t>-33,56; 57,34</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-71,17; 0,0</t>
+          <t>-70,17; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 128,51</t>
+          <t>-24,86; 130,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,2; 141,36</t>
+          <t>-37,79; 134,9</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,44</t>
+          <t>0,0; 36,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,2</t>
+          <t>0,0; 37,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 8,69</t>
+          <t>-21,51; 8,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 8,49</t>
+          <t>-17,23; 8,77</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,54</t>
+          <t>0,0; 58,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,86</t>
+          <t>0,0; 60,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 9,48</t>
+          <t>-21,64; 9,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 9,28</t>
+          <t>-17,54; 9,6</t>
         </is>
       </c>
     </row>
